--- a/output/北塩原村_地域生活支援事業.xlsx
+++ b/output/北塩原村_地域生活支援事業.xlsx
@@ -1261,7 +1261,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>法第77条第1項第6号</t>
+          <t>法第77条第1項第7号</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>法第77条第1項第6号</t>
+          <t>法第77条第1項第7号</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>法第77条第1項第6号</t>
+          <t>法第77条第1項第7号</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>法第77条第1項第6号</t>
+          <t>法第77条第1項第7号</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>法第77条第1項第6号</t>
+          <t>法第77条第1項第7号</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>法第77条第1項第6号</t>
+          <t>法第77条第1項第7号</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>法第77条第1項第7号</t>
+          <t>法第77条第1項第8号</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>法第77条第1項第8号</t>
+          <t>法第77条第1項第9号</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>法第77条第1項第9号</t>
+          <t>法第77条第1項第10号</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">

--- a/output/北塩原村_地域生活支援事業.xlsx
+++ b/output/北塩原村_地域生活支援事業.xlsx
@@ -1197,7 +1197,7 @@
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>現行計画は事業内容欄には記載があるが、実績・見込量の表に行がない。次期計画では表に加えるか、実施しない旨を明記するかを整理する</t>
+          <t>現行計画も次期計画の正本も、事業内容欄には記載があるが実績・見込量の表に行がない。①事業として行うなら年度ごとの件数を表に加える、②実施しないならその旨と成年後見制度の利用支援をどの事業で担うかを明記する、の二者で整理する（Ｍ-114）</t>
         </is>
       </c>
     </row>
@@ -1903,12 +1903,12 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>現行計画は事業内容欄に記載があるが、実績・見込量の表に現れない。実施していないのか、実施しているが計上漏れなのかが判別できない</t>
+          <t>次期計画の正本でも同じ状態が続いている。事業内容欄（第5章3）には⑤成年後見制度法人後見支援事業・⑧手話奉仕員養成研修事業として記載があるが、表5-29（実績）・表5-30（見込量）はいずれも17行で、法人後見支援事業の行がない（手話奉仕員養成研修事業は0人として行がある）。告示 第三 二 3 ㈡は事業の種類ごとに実施に関する考え方と量の見込みを定めることとしており、内容に掲げながら量を示さない状態は、実施していないのか計上していないのかが読み取れない</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>村へ確認。次期計画では表に加えるか、実施しない旨を明記する</t>
+          <t>令和8年10月13日に正本 第5章3 へ、①事業として行うなら年度ごとの件数を表に加える、②実施しないならその旨と成年後見制度の利用支援をどの事業で担うかを明記する、の二者で整理する記述を入れた（ＲＶ-2）。どちらを選ぶかを村へ照会（Ｍ-114）。手話奉仕員養成研修事業は0人の見込量の妥当性をＭ-59・Ｍ-60で照会済み</t>
         </is>
       </c>
     </row>
